--- a/Planilhas/Pedidos.xlsx
+++ b/Planilhas/Pedidos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junio\OneDrive\Área de Trabalho\Documentos\Scripts Github\automations\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEB8E9A-82EB-4450-9E02-0D1E010F3908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB238E02-C775-4C0C-96D3-276DE407678A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERAR PARA F5" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -53,10 +42,10 @@
     <t>Modo</t>
   </si>
   <si>
-    <t>AMBOS</t>
+    <t>F4</t>
   </si>
   <si>
-    <t>F4</t>
+    <t>RAZAO</t>
   </si>
 </sst>
 </file>
@@ -67,19 +56,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -229,39 +218,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -313,7 +302,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -424,6 +413,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -432,13 +428,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -503,31 +492,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -536,16 +505,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
   <dimension ref="A1:E62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="4" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -562,7 +531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4500030627</v>
       </c>
@@ -570,16 +539,16 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>3201010111</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4500030628</v>
       </c>
@@ -587,16 +556,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>3201010111</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4500030629</v>
       </c>
@@ -604,16 +573,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>3201010111</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4500030630</v>
       </c>
@@ -621,16 +590,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>3201010111</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4500030631</v>
       </c>
@@ -638,16 +607,16 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>3201010111</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4500030632</v>
       </c>
@@ -655,16 +624,16 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>3201010111</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4500030633</v>
       </c>
@@ -672,16 +641,16 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>3201010111</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4500030634</v>
       </c>
@@ -689,16 +658,16 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>3201010111</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>4500030635</v>
       </c>
@@ -706,16 +675,16 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>3201010111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>4500030638</v>
       </c>
@@ -723,16 +692,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>3201010111</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>4500030639</v>
       </c>
@@ -740,16 +709,16 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>3201010111</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4500030640</v>
       </c>
@@ -757,16 +726,16 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>3201010111</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4500030641</v>
       </c>
@@ -774,16 +743,16 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>3201010111</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4500030642</v>
       </c>
@@ -791,16 +760,16 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>3201010111</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>4500030643</v>
       </c>
@@ -808,16 +777,16 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>3201010111</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4500030646</v>
       </c>
@@ -825,16 +794,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>3201010111</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>4500030647</v>
       </c>
@@ -842,16 +811,16 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>3201010111</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>4500030648</v>
       </c>
@@ -859,16 +828,16 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>3201010111</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4500030649</v>
       </c>
@@ -876,16 +845,16 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>3201010111</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4500030650</v>
       </c>
@@ -893,16 +862,16 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>3201010111</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4500030651</v>
       </c>
@@ -910,16 +879,16 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>3201010111</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>4500030652</v>
       </c>
@@ -927,16 +896,16 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>3201010111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4500030653</v>
       </c>
@@ -944,16 +913,16 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>3201010111</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4500030656</v>
       </c>
@@ -961,16 +930,16 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>3201010111</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4500030657</v>
       </c>
@@ -978,16 +947,16 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>3201010111</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4500030671</v>
       </c>
@@ -995,16 +964,16 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>3201010111</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4500030672</v>
       </c>
@@ -1012,16 +981,16 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>3201010111</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4500030673</v>
       </c>
@@ -1029,16 +998,16 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>3201010111</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4500030674</v>
       </c>
@@ -1046,16 +1015,16 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>3201010111</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4500030675</v>
       </c>
@@ -1063,16 +1032,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>3201010111</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>4500030676</v>
       </c>
@@ -1080,16 +1049,16 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>3201010111</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4500030677</v>
       </c>
@@ -1097,16 +1066,16 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>3201010111</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>4500030678</v>
       </c>
@@ -1114,16 +1083,16 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>3201010111</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4500030679</v>
       </c>
@@ -1131,16 +1100,16 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>3201010111</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>4500030680</v>
       </c>
@@ -1148,16 +1117,16 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>3201010111</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4500030681</v>
       </c>
@@ -1165,16 +1134,16 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>3201010111</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>4500030682</v>
       </c>
@@ -1182,16 +1151,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>3201010111</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>4500030683</v>
       </c>
@@ -1199,16 +1168,16 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>3201010111</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>4500030684</v>
       </c>
@@ -1216,16 +1185,16 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>3201010111</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4500030685</v>
       </c>
@@ -1233,16 +1202,16 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>3201010111</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>4500030686</v>
       </c>
@@ -1250,16 +1219,16 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>3201010111</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>4500030687</v>
       </c>
@@ -1267,16 +1236,16 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>3201010111</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>4500030688</v>
       </c>
@@ -1284,16 +1253,16 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>3201010111</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4500030689</v>
       </c>
@@ -1301,16 +1270,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>3201010111</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>4500030690</v>
       </c>
@@ -1318,16 +1287,16 @@
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>3201010111</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4500030692</v>
       </c>
@@ -1335,16 +1304,16 @@
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>3201010111</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>4500030693</v>
       </c>
@@ -1352,16 +1321,16 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>3201010111</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>4500030694</v>
       </c>
@@ -1369,16 +1338,16 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>3201010111</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4500030695</v>
       </c>
@@ -1386,16 +1355,16 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>3201010111</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>4500030715</v>
       </c>
@@ -1403,16 +1372,16 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51">
         <v>3201010111</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>4500030716</v>
       </c>
@@ -1420,16 +1389,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52">
         <v>3201010111</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>4500030717</v>
       </c>
@@ -1437,16 +1406,16 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>3201010111</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>4500030718</v>
       </c>
@@ -1454,16 +1423,16 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>3201010111</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>4500030720</v>
       </c>
@@ -1471,16 +1440,16 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>3201010111</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>4500030721</v>
       </c>
@@ -1488,16 +1457,16 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56">
         <v>3201010111</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>4500030722</v>
       </c>
@@ -1505,16 +1474,16 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>3201010111</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>4500030723</v>
       </c>
@@ -1522,16 +1491,16 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58">
         <v>3201010111</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4500030724</v>
       </c>
@@ -1539,16 +1508,16 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>3201010111</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>4500030725</v>
       </c>
@@ -1556,16 +1525,16 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>3201010111</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>4500030726</v>
       </c>
@@ -1573,16 +1542,16 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>3201010111</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>4500030727</v>
       </c>
@@ -1590,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62">
         <v>3201010111</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Planilhas/Pedidos.xlsx
+++ b/Planilhas/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junio\OneDrive\Área de Trabalho\Documentos\Scripts Github\automations\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB238E02-C775-4C0C-96D3-276DE407678A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B480C3F-9A5F-4508-A324-37BA6465DC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="7">
   <si>
     <t>Item</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Modo</t>
   </si>
   <si>
-    <t>F4</t>
+    <t>F5</t>
   </si>
   <si>
     <t>RAZAO</t>
@@ -194,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E62" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:E62" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E37" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:E37" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos"/>
     <tableColumn id="2" xr3:uid="{3D9316E3-CFBE-4A9E-8B75-E0BF8E30E135}" name="Item" dataDxfId="3"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -533,7 +533,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4500030627</v>
+        <v>4500031354</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4500030628</v>
+        <v>4500031355</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4500030629</v>
+        <v>4500031356</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -584,7 +584,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4500030630</v>
+        <v>4500031357</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4500030631</v>
+        <v>4500031358</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4500030632</v>
+        <v>4500031368</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>4500030633</v>
+        <v>4500031369</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -652,7 +652,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>4500030634</v>
+        <v>4500031377</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>4500030635</v>
+        <v>4500031378</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>4500030638</v>
+        <v>4500031379</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4500030639</v>
+        <v>4500031380</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4500030640</v>
+        <v>4500031383</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4500030641</v>
+        <v>4500031385</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>4500030642</v>
+        <v>4500031386</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>4500030643</v>
+        <v>4500031387</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>4500030646</v>
+        <v>4500031388</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>4500030647</v>
+        <v>4500031389</v>
       </c>
       <c r="B18">
         <v>10</v>
@@ -822,7 +822,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>4500030648</v>
+        <v>4500031390</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>4500030649</v>
+        <v>4500031422</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>4500030650</v>
+        <v>4500031423</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>4500030651</v>
+        <v>4500031424</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4500030652</v>
+        <v>4500031425</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4500030653</v>
+        <v>4500031426</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -924,7 +924,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>4500030656</v>
+        <v>4500031427</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4500030657</v>
+        <v>4500031428</v>
       </c>
       <c r="B26">
         <v>10</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4500030671</v>
+        <v>4500031429</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4500030672</v>
+        <v>4500031430</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4500030673</v>
+        <v>4500031431</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>4500030674</v>
+        <v>4500031432</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4500030675</v>
+        <v>4500031433</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>4500030676</v>
+        <v>4500031434</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>4500030677</v>
+        <v>4500031435</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1077,7 +1077,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>4500030678</v>
+        <v>4500031436</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>4500030679</v>
+        <v>4500031437</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>4500030680</v>
+        <v>4500031438</v>
       </c>
       <c r="B36">
         <v>10</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>4500030681</v>
+        <v>4500031439</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -1140,431 +1140,6 @@
         <v>3201010111</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>4500030682</v>
-      </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38">
-        <v>3201010111</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>4500030683</v>
-      </c>
-      <c r="B39">
-        <v>10</v>
-      </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39">
-        <v>3201010111</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>4500030684</v>
-      </c>
-      <c r="B40">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40">
-        <v>3201010111</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>4500030685</v>
-      </c>
-      <c r="B41">
-        <v>10</v>
-      </c>
-      <c r="C41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41">
-        <v>3201010111</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>4500030686</v>
-      </c>
-      <c r="B42">
-        <v>10</v>
-      </c>
-      <c r="C42" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42">
-        <v>3201010111</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>4500030687</v>
-      </c>
-      <c r="B43">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43">
-        <v>3201010111</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>4500030688</v>
-      </c>
-      <c r="B44">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44">
-        <v>3201010111</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>4500030689</v>
-      </c>
-      <c r="B45">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45">
-        <v>3201010111</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>4500030690</v>
-      </c>
-      <c r="B46">
-        <v>10</v>
-      </c>
-      <c r="C46" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46">
-        <v>3201010111</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>4500030692</v>
-      </c>
-      <c r="B47">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47">
-        <v>3201010111</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>4500030693</v>
-      </c>
-      <c r="B48">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48">
-        <v>3201010111</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>4500030694</v>
-      </c>
-      <c r="B49">
-        <v>10</v>
-      </c>
-      <c r="C49" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49">
-        <v>3201010111</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>4500030695</v>
-      </c>
-      <c r="B50">
-        <v>10</v>
-      </c>
-      <c r="C50" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50">
-        <v>3201010111</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>4500030715</v>
-      </c>
-      <c r="B51">
-        <v>10</v>
-      </c>
-      <c r="C51" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51">
-        <v>3201010111</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>4500030716</v>
-      </c>
-      <c r="B52">
-        <v>10</v>
-      </c>
-      <c r="C52" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52">
-        <v>3201010111</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>4500030717</v>
-      </c>
-      <c r="B53">
-        <v>10</v>
-      </c>
-      <c r="C53" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53">
-        <v>3201010111</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>4500030718</v>
-      </c>
-      <c r="B54">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54">
-        <v>3201010111</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>4500030720</v>
-      </c>
-      <c r="B55">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55">
-        <v>3201010111</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>4500030721</v>
-      </c>
-      <c r="B56">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56">
-        <v>3201010111</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>4500030722</v>
-      </c>
-      <c r="B57">
-        <v>10</v>
-      </c>
-      <c r="C57" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57">
-        <v>3201010111</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>4500030723</v>
-      </c>
-      <c r="B58">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58">
-        <v>3201010111</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>4500030724</v>
-      </c>
-      <c r="B59">
-        <v>10</v>
-      </c>
-      <c r="C59" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59">
-        <v>3201010111</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>4500030725</v>
-      </c>
-      <c r="B60">
-        <v>10</v>
-      </c>
-      <c r="C60" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60">
-        <v>3201010111</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>4500030726</v>
-      </c>
-      <c r="B61">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61">
-        <v>3201010111</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>4500030727</v>
-      </c>
-      <c r="B62">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62">
-        <v>3201010111</v>
-      </c>
-      <c r="E62" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Planilhas/Pedidos.xlsx
+++ b/Planilhas/Pedidos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junio\OneDrive\Área de Trabalho\Documentos\Scripts Github\automations\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B480C3F-9A5F-4508-A324-37BA6465DC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43B6BC3-7770-48A4-8A5D-ED55470FE0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERAR PARA F5" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="7">
   <si>
     <t>Item</t>
   </si>
@@ -194,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E37" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:E37" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E73" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:E73" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos"/>
     <tableColumn id="2" xr3:uid="{3D9316E3-CFBE-4A9E-8B75-E0BF8E30E135}" name="Item" dataDxfId="3"/>
@@ -208,9 +208,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -248,7 +248,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -354,7 +354,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -496,7 +496,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -504,17 +504,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E73"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -531,9 +531,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>4500031354</v>
+        <v>4500032148</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -548,9 +548,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>4500031355</v>
+        <v>4500032149</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -565,9 +565,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>4500031356</v>
+        <v>4500032178</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -582,9 +582,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>4500031357</v>
+        <v>4500032140</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -599,9 +599,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>4500031358</v>
+        <v>4500032143</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -616,9 +616,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>4500031368</v>
+        <v>4500032145</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -633,9 +633,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>4500031369</v>
+        <v>4500032185</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -650,9 +650,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>4500031377</v>
+        <v>4500032186</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -667,9 +667,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>4500031378</v>
+        <v>4500032207</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -684,9 +684,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>4500031379</v>
+        <v>4500032208</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -701,9 +701,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>4500031380</v>
+        <v>4500032177</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -718,9 +718,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>4500031383</v>
+        <v>4500032142</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -735,9 +735,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>4500031385</v>
+        <v>4500032201</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -752,9 +752,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>4500031386</v>
+        <v>4500032168</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -769,9 +769,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>4500031387</v>
+        <v>4500032169</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -786,9 +786,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>4500031388</v>
+        <v>4500032147</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -803,9 +803,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>4500031389</v>
+        <v>4500032204</v>
       </c>
       <c r="B18">
         <v>10</v>
@@ -820,9 +820,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>4500031390</v>
+        <v>4500032210</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -837,9 +837,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>4500031422</v>
+        <v>4500032184</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -854,9 +854,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>4500031423</v>
+        <v>4500032203</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -871,9 +871,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>4500031424</v>
+        <v>4500032211</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -888,9 +888,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>4500031425</v>
+        <v>4500032167</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -905,9 +905,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>4500031426</v>
+        <v>4500032205</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -922,9 +922,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>4500031427</v>
+        <v>4500032209</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -939,9 +939,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>4500031428</v>
+        <v>4500032170</v>
       </c>
       <c r="B26">
         <v>10</v>
@@ -956,9 +956,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>4500031429</v>
+        <v>4500032183</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -973,9 +973,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>4500031430</v>
+        <v>4500032202</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -990,9 +990,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>4500031431</v>
+        <v>4500032206</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -1007,9 +1007,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>4500031432</v>
+        <v>4500032152</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -1024,9 +1024,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>4500031433</v>
+        <v>4500032153</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -1041,9 +1041,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>4500031434</v>
+        <v>4500032154</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -1058,9 +1058,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>4500031435</v>
+        <v>4500032155</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1075,9 +1075,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>4500031436</v>
+        <v>4500032156</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -1092,9 +1092,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>4500031437</v>
+        <v>4500032157</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -1109,9 +1109,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>4500031438</v>
+        <v>4500032158</v>
       </c>
       <c r="B36">
         <v>10</v>
@@ -1126,9 +1126,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>4500031439</v>
+        <v>4500032159</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -1140,6 +1140,618 @@
         <v>3201010111</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>4500032160</v>
+      </c>
+      <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>3201010111</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4500032161</v>
+      </c>
+      <c r="B39">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39">
+        <v>3201010111</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>4500032162</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40">
+        <v>3201010111</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4500032163</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>3201010111</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4500032165</v>
+      </c>
+      <c r="B42">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>3201010111</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>4500032166</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43">
+        <v>3201010111</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>4500032171</v>
+      </c>
+      <c r="B44">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44">
+        <v>3201010111</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4500032172</v>
+      </c>
+      <c r="B45">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45">
+        <v>3201010111</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>4500032173</v>
+      </c>
+      <c r="B46">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>3201010111</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>4500032174</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>3201010111</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>4500032175</v>
+      </c>
+      <c r="B48">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48">
+        <v>3201010111</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>4500032176</v>
+      </c>
+      <c r="B49">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49">
+        <v>3201010111</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4500032180</v>
+      </c>
+      <c r="B50">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>3201010111</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>4500032181</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51">
+        <v>3201010111</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>4500032182</v>
+      </c>
+      <c r="B52">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>3201010111</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4500032187</v>
+      </c>
+      <c r="B53">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>3201010111</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>4500032188</v>
+      </c>
+      <c r="B54">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54">
+        <v>3201010111</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>4500032189</v>
+      </c>
+      <c r="B55">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55">
+        <v>3201010111</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>4500032190</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56">
+        <v>3201010111</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>4500032191</v>
+      </c>
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57">
+        <v>3201010111</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>4500032192</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58">
+        <v>3201010111</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4500032193</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59">
+        <v>3201010111</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4500032194</v>
+      </c>
+      <c r="B60">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60">
+        <v>3201010111</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>4500032195</v>
+      </c>
+      <c r="B61">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61">
+        <v>3201010111</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>4500032196</v>
+      </c>
+      <c r="B62">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62">
+        <v>3201010111</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>4500032197</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>3201010111</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>4500032198</v>
+      </c>
+      <c r="B64">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64">
+        <v>3201010111</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>4500032199</v>
+      </c>
+      <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <v>3201010111</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>4500032200</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>3201010111</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>4500032212</v>
+      </c>
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>3201010111</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>4500032213</v>
+      </c>
+      <c r="B68">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>3201010111</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>4500032214</v>
+      </c>
+      <c r="B69">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>3201010111</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>4500032215</v>
+      </c>
+      <c r="B70">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70">
+        <v>3201010111</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>4500032216</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>3201010111</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>4500032217</v>
+      </c>
+      <c r="B72">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72">
+        <v>3201010111</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>4500032218</v>
+      </c>
+      <c r="B73">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73">
+        <v>3201010111</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Planilhas/Pedidos.xlsx
+++ b/Planilhas/Pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43B6BC3-7770-48A4-8A5D-ED55470FE0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4580F128-32A3-4917-8AEE-614E4FF606D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="7">
   <si>
     <t>Item</t>
   </si>
@@ -194,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E73" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:E73" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E68" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:E68" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos"/>
     <tableColumn id="2" xr3:uid="{3D9316E3-CFBE-4A9E-8B75-E0BF8E30E135}" name="Item" dataDxfId="3"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -533,7 +533,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>4500032148</v>
+        <v>4500033536</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>4500032149</v>
+        <v>4500033802</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>4500032178</v>
+        <v>4500033803</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -584,7 +584,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>4500032140</v>
+        <v>4500033804</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>4500032143</v>
+        <v>4500033805</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>4500032145</v>
+        <v>4500033812</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>4500032185</v>
+        <v>4500033813</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -652,7 +652,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>4500032186</v>
+        <v>4500033814</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>4500032207</v>
+        <v>4500033815</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>4500032208</v>
+        <v>4500033816</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>4500032177</v>
+        <v>4500033817</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>4500032142</v>
+        <v>4500033818</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>4500032201</v>
+        <v>4500033819</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>4500032168</v>
+        <v>4500033820</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>4500032169</v>
+        <v>4500033821</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>4500032147</v>
+        <v>4500033827</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>4500032204</v>
+        <v>4500033829</v>
       </c>
       <c r="B18">
         <v>10</v>
@@ -822,7 +822,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>4500032210</v>
+        <v>4500033831</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>4500032184</v>
+        <v>4500033832</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>4500032203</v>
+        <v>4500033833</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>4500032211</v>
+        <v>4500033835</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>4500032167</v>
+        <v>4500033836</v>
       </c>
       <c r="B23">
         <v>10</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>4500032205</v>
+        <v>4500033837</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -924,7 +924,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>4500032209</v>
+        <v>4500033841</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>4500032170</v>
+        <v>4500033851</v>
       </c>
       <c r="B26">
         <v>10</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>4500032183</v>
+        <v>4500033852</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>4500032202</v>
+        <v>4500033853</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>4500032206</v>
+        <v>4500033854</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>4500032152</v>
+        <v>4500033855</v>
       </c>
       <c r="B30">
         <v>10</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>4500032153</v>
+        <v>4500033856</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>4500032154</v>
+        <v>4500033857</v>
       </c>
       <c r="B32">
         <v>10</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>4500032155</v>
+        <v>4500033858</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1077,7 +1077,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>4500032156</v>
+        <v>4500033859</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>4500032157</v>
+        <v>4500033860</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>4500032158</v>
+        <v>4500033861</v>
       </c>
       <c r="B36">
         <v>10</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>4500032159</v>
+        <v>4500033862</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>4500032160</v>
+        <v>4500033863</v>
       </c>
       <c r="B38">
         <v>10</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>4500032161</v>
+        <v>4500033864</v>
       </c>
       <c r="B39">
         <v>10</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>4500032162</v>
+        <v>4500033872</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>4500032163</v>
+        <v>4500033874</v>
       </c>
       <c r="B41">
         <v>10</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>4500032165</v>
+        <v>4500033875</v>
       </c>
       <c r="B42">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>4500032166</v>
+        <v>4500033876</v>
       </c>
       <c r="B43">
         <v>10</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>4500032171</v>
+        <v>4500033877</v>
       </c>
       <c r="B44">
         <v>10</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>4500032172</v>
+        <v>4500033878</v>
       </c>
       <c r="B45">
         <v>10</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>4500032173</v>
+        <v>4500033801</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>4500032174</v>
+        <v>4500033822</v>
       </c>
       <c r="B47">
         <v>10</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>4500032175</v>
+        <v>4500033823</v>
       </c>
       <c r="B48">
         <v>10</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>4500032176</v>
+        <v>4500033824</v>
       </c>
       <c r="B49">
         <v>10</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>4500032180</v>
+        <v>4500033825</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>4500032181</v>
+        <v>4500033826</v>
       </c>
       <c r="B51">
         <v>10</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>4500032182</v>
+        <v>4500033838</v>
       </c>
       <c r="B52">
         <v>10</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>4500032187</v>
+        <v>4500033839</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>4500032188</v>
+        <v>4500033840</v>
       </c>
       <c r="B54">
         <v>10</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>4500032189</v>
+        <v>4500033842</v>
       </c>
       <c r="B55">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>4500032190</v>
+        <v>4500033843</v>
       </c>
       <c r="B56">
         <v>10</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>4500032191</v>
+        <v>4500033844</v>
       </c>
       <c r="B57">
         <v>10</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>4500032192</v>
+        <v>4500033846</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>4500032193</v>
+        <v>4500033847</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>4500032194</v>
+        <v>4500033848</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>4500032195</v>
+        <v>4500033849</v>
       </c>
       <c r="B61">
         <v>10</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>4500032196</v>
+        <v>4500033850</v>
       </c>
       <c r="B62">
         <v>10</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>4500032197</v>
+        <v>4500033865</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>4500032198</v>
+        <v>4500033866</v>
       </c>
       <c r="B64">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>4500032199</v>
+        <v>4500033867</v>
       </c>
       <c r="B65">
         <v>10</v>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>4500032200</v>
+        <v>4500033868</v>
       </c>
       <c r="B66">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>4500032212</v>
+        <v>4500033869</v>
       </c>
       <c r="B67">
         <v>10</v>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>4500032213</v>
+        <v>4500033870</v>
       </c>
       <c r="B68">
         <v>10</v>
@@ -1667,91 +1667,6 @@
         <v>3201010111</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>4500032214</v>
-      </c>
-      <c r="B69">
-        <v>10</v>
-      </c>
-      <c r="C69" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69">
-        <v>3201010111</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>4500032215</v>
-      </c>
-      <c r="B70">
-        <v>10</v>
-      </c>
-      <c r="C70" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70">
-        <v>3201010111</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>4500032216</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
-      </c>
-      <c r="C71" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71">
-        <v>3201010111</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>4500032217</v>
-      </c>
-      <c r="B72">
-        <v>10</v>
-      </c>
-      <c r="C72" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72">
-        <v>3201010111</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>4500032218</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73">
-        <v>3201010111</v>
-      </c>
-      <c r="E73" s="2" t="s">
         <v>6</v>
       </c>
     </row>
